--- a/GunfireDungeon_Godot/excelTool/excel/Test.xlsx
+++ b/GunfireDungeon_Godot/excelTool/excel/Test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24765" windowHeight="14685"/>
+    <workbookView windowHeight="18800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="84">
   <si>
     <t>Id</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>RefValue2</t>
+  </si>
+  <si>
+    <t>CustomExpr</t>
+  </si>
+  <si>
+    <t>CustomExprNotes</t>
   </si>
   <si>
     <t>唯一id</t>
@@ -156,6 +162,13 @@
     <t>引用其他单元格数据</t>
   </si>
   <si>
+    <t>自定义表达式类型
+可以用做计算公式</t>
+  </si>
+  <si>
+    <t>对于前面一列的表达式解释</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -208,6 +221,9 @@
   </si>
   <si>
     <t>[string]*</t>
+  </si>
+  <si>
+    <t>Expr</t>
   </si>
   <si>
     <t>0001</t>
@@ -423,7 +439,16 @@
 "${Table2.item_0001.Name}$"</t>
   </si>
   <si>
+    <t>{a}+{b}*{a}</t>
+  </si>
+  <si>
     <t>0002</t>
+  </si>
+  <si>
+    <t>{a:int}+{b}*{a}</t>
+  </si>
+  <si>
+    <t>int:{a}+{b:int}</t>
   </si>
 </sst>
 </file>
@@ -1112,20 +1137,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1136,6 +1161,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1488,48 +1516,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AS5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:AS7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
-    <col min="3" max="3" width="9.30833333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.1083333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.775" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.725" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.1666666666667" style="2" customWidth="1"/>
-    <col min="9" max="9" width="25.8333333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.6333333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.6583333333333" style="2" customWidth="1"/>
-    <col min="12" max="13" width="19.5833333333333" style="2" customWidth="1"/>
-    <col min="14" max="14" width="21.3333333333333" style="2" customWidth="1"/>
-    <col min="15" max="15" width="24.8916666666667" style="2" customWidth="1"/>
-    <col min="16" max="16" width="21.6666666666667" style="2" customWidth="1"/>
-    <col min="17" max="17" width="24.5833333333333" customWidth="1"/>
-    <col min="18" max="18" width="34.575" style="2" customWidth="1"/>
-    <col min="19" max="19" width="33.05" style="2" customWidth="1"/>
-    <col min="20" max="20" width="31.9416666666667" style="2" customWidth="1"/>
-    <col min="22" max="22" width="21" style="2" customWidth="1"/>
-    <col min="23" max="23" width="15.6666666666667" style="2" customWidth="1"/>
-    <col min="24" max="24" width="23.775" style="2" customWidth="1"/>
-    <col min="25" max="25" width="24.1083333333333" style="2" customWidth="1"/>
-    <col min="26" max="26" width="25.8916666666667" style="2" customWidth="1"/>
-    <col min="27" max="27" width="24.775" style="2" customWidth="1"/>
-    <col min="28" max="28" width="28.8916666666667" style="2" customWidth="1"/>
-    <col min="29" max="29" width="17.3333333333333" style="2" customWidth="1"/>
-    <col min="30" max="30" width="17.775" style="2" customWidth="1"/>
-    <col min="31" max="31" width="19.0083333333333" style="2" customWidth="1"/>
-    <col min="32" max="32" width="20" style="2" customWidth="1"/>
-    <col min="33" max="33" width="30.9833333333333" style="2" customWidth="1"/>
-    <col min="34" max="34" width="22.9666666666667" style="2" customWidth="1"/>
-    <col min="35" max="35" width="23.7" style="2" customWidth="1"/>
-    <col min="36" max="36" width="27.65" style="2" customWidth="1"/>
-    <col min="37" max="37" width="27.775" style="2" customWidth="1"/>
-    <col min="38" max="38" width="24.075" style="2" customWidth="1"/>
-    <col min="39" max="41" width="9" style="2"/>
+    <col min="3" max="3" width="9.30769230769231" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.1057692307692" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.7788461538462" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.3365384615385" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.72115384615385" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.1634615384615" style="3" customWidth="1"/>
+    <col min="9" max="9" width="25.8365384615385" style="3" customWidth="1"/>
+    <col min="10" max="10" width="17.6346153846154" style="3" customWidth="1"/>
+    <col min="11" max="11" width="21.6538461538462" style="3" customWidth="1"/>
+    <col min="12" max="13" width="19.5865384615385" style="3" customWidth="1"/>
+    <col min="14" max="14" width="21.3365384615385" style="3" customWidth="1"/>
+    <col min="15" max="15" width="24.8942307692308" style="3" customWidth="1"/>
+    <col min="16" max="16" width="21.6634615384615" style="3" customWidth="1"/>
+    <col min="17" max="17" width="24.5865384615385" customWidth="1"/>
+    <col min="18" max="18" width="34.5769230769231" style="3" customWidth="1"/>
+    <col min="19" max="19" width="33.0480769230769" style="3" customWidth="1"/>
+    <col min="20" max="20" width="31.9423076923077" style="3" customWidth="1"/>
+    <col min="21" max="21" width="42.5576923076923" customWidth="1"/>
+    <col min="22" max="22" width="21" style="3" customWidth="1"/>
+    <col min="23" max="23" width="15.6634615384615" style="3" customWidth="1"/>
+    <col min="24" max="24" width="23.7788461538462" style="3" customWidth="1"/>
+    <col min="25" max="25" width="24.1057692307692" style="3" customWidth="1"/>
+    <col min="26" max="26" width="25.8942307692308" style="3" customWidth="1"/>
+    <col min="27" max="27" width="24.7788461538462" style="3" customWidth="1"/>
+    <col min="28" max="28" width="28.8942307692308" style="3" customWidth="1"/>
+    <col min="29" max="29" width="17.3365384615385" style="3" customWidth="1"/>
+    <col min="30" max="30" width="17.7788461538462" style="3" customWidth="1"/>
+    <col min="31" max="31" width="19.0096153846154" style="3" customWidth="1"/>
+    <col min="32" max="32" width="20" style="3" customWidth="1"/>
+    <col min="33" max="33" width="30.9807692307692" style="3" customWidth="1"/>
+    <col min="34" max="34" width="22.9711538461538" style="3" customWidth="1"/>
+    <col min="35" max="35" width="23.7019230769231" style="3" customWidth="1"/>
+    <col min="36" max="36" width="27.6538461538462" style="3" customWidth="1"/>
+    <col min="37" max="37" width="27.7788461538462" style="3" customWidth="1"/>
+    <col min="38" max="38" width="24.0769230769231" style="3" customWidth="1"/>
+    <col min="39" max="41" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31" customHeight="1" spans="1:20">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="31" customHeight="1" spans="1:22">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1547,183 +1576,201 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" ht="154" customHeight="1" spans="1:45">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
+      <c r="A2" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="O2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
+      <c r="S2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3"/>
+      <c r="AR2" s="3"/>
+      <c r="AS2" s="3"/>
     </row>
-    <row r="3" ht="27" customHeight="1" spans="1:20">
-      <c r="A3" s="2" t="s">
-        <v>39</v>
+    <row r="3" ht="27" customHeight="1" spans="1:22">
+      <c r="A3" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>54</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>56</v>
+      <c r="T3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="U3" t="s">
+        <v>61</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="4" ht="110" customHeight="1" spans="1:20">
+    <row r="4" ht="110" customHeight="1" spans="1:21">
       <c r="A4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C4" s="1">
         <v>12.3</v>
@@ -1732,62 +1779,76 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>69</v>
       </c>
+      <c r="K4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="P4" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Q4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="U4" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="5" ht="49" customHeight="1" spans="1:17">
-      <c r="A5" s="8" t="s">
-        <v>75</v>
+    <row r="5" ht="49" customHeight="1" spans="1:21">
+      <c r="A5" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
       </c>
       <c r="Q5" s="7"/>
+      <c r="U5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="21:21">
+      <c r="U6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="21:21">
+      <c r="U7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1800,46 +1861,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C2:J5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <sheetData>
     <row r="2" spans="3:10">
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="3:10">
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
     </row>
     <row r="4" spans="3:10">
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
     </row>
     <row r="5" spans="3:9">
-      <c r="C5" s="3"/>
+      <c r="C5" s="2"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1852,7 +1913,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/GunfireDungeon_Godot/excelTool/excel/Test.xlsx
+++ b/GunfireDungeon_Godot/excelTool/excel/Test.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -89,12 +89,6 @@
   </si>
   <si>
     <t>RefValue2</t>
-  </si>
-  <si>
-    <t>CustomExpr</t>
-  </si>
-  <si>
-    <t>CustomExprNotes</t>
   </si>
   <si>
     <t>唯一id</t>
@@ -162,13 +156,6 @@
     <t>引用其他单元格数据</t>
   </si>
   <si>
-    <t>自定义表达式类型
-可以用做计算公式</t>
-  </si>
-  <si>
-    <t>对于前面一列的表达式解释</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -221,9 +208,6 @@
   </si>
   <si>
     <t>[string]*</t>
-  </si>
-  <si>
-    <t>Expr</t>
   </si>
   <si>
     <t>0001</t>
@@ -439,16 +423,7 @@
 "${Table2.item_0001.Name}$"</t>
   </si>
   <si>
-    <t>{a}+{b}*{a}</t>
-  </si>
-  <si>
     <t>0002</t>
-  </si>
-  <si>
-    <t>{a:int}+{b}*{a}</t>
-  </si>
-  <si>
-    <t>int:{a}+{b:int}</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1112,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1161,9 +1136,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1516,8 +1488,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AS7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="A1:AQ5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
     <col min="3" max="3" width="9.30769230769231" style="3" customWidth="1"/>
     <col min="4" max="4" width="11.1057692307692" style="3" customWidth="1"/>
@@ -1536,28 +1508,26 @@
     <col min="18" max="18" width="34.5769230769231" style="3" customWidth="1"/>
     <col min="19" max="19" width="33.0480769230769" style="3" customWidth="1"/>
     <col min="20" max="20" width="31.9423076923077" style="3" customWidth="1"/>
-    <col min="21" max="21" width="42.5576923076923" customWidth="1"/>
-    <col min="22" max="22" width="21" style="3" customWidth="1"/>
-    <col min="23" max="23" width="15.6634615384615" style="3" customWidth="1"/>
-    <col min="24" max="24" width="23.7788461538462" style="3" customWidth="1"/>
-    <col min="25" max="25" width="24.1057692307692" style="3" customWidth="1"/>
-    <col min="26" max="26" width="25.8942307692308" style="3" customWidth="1"/>
-    <col min="27" max="27" width="24.7788461538462" style="3" customWidth="1"/>
-    <col min="28" max="28" width="28.8942307692308" style="3" customWidth="1"/>
-    <col min="29" max="29" width="17.3365384615385" style="3" customWidth="1"/>
-    <col min="30" max="30" width="17.7788461538462" style="3" customWidth="1"/>
-    <col min="31" max="31" width="19.0096153846154" style="3" customWidth="1"/>
-    <col min="32" max="32" width="20" style="3" customWidth="1"/>
-    <col min="33" max="33" width="30.9807692307692" style="3" customWidth="1"/>
-    <col min="34" max="34" width="22.9711538461538" style="3" customWidth="1"/>
-    <col min="35" max="35" width="23.7019230769231" style="3" customWidth="1"/>
-    <col min="36" max="36" width="27.6538461538462" style="3" customWidth="1"/>
-    <col min="37" max="37" width="27.7788461538462" style="3" customWidth="1"/>
-    <col min="38" max="38" width="24.0769230769231" style="3" customWidth="1"/>
-    <col min="39" max="41" width="9" style="3"/>
+    <col min="21" max="21" width="15.6634615384615" style="3" customWidth="1"/>
+    <col min="22" max="22" width="23.7788461538462" style="3" customWidth="1"/>
+    <col min="23" max="23" width="24.1057692307692" style="3" customWidth="1"/>
+    <col min="24" max="24" width="25.8942307692308" style="3" customWidth="1"/>
+    <col min="25" max="25" width="24.7788461538462" style="3" customWidth="1"/>
+    <col min="26" max="26" width="28.8942307692308" style="3" customWidth="1"/>
+    <col min="27" max="27" width="17.3365384615385" style="3" customWidth="1"/>
+    <col min="28" max="28" width="17.7788461538462" style="3" customWidth="1"/>
+    <col min="29" max="29" width="19.0096153846154" style="3" customWidth="1"/>
+    <col min="30" max="30" width="20" style="3" customWidth="1"/>
+    <col min="31" max="31" width="30.9807692307692" style="3" customWidth="1"/>
+    <col min="32" max="32" width="22.9711538461538" style="3" customWidth="1"/>
+    <col min="33" max="33" width="23.7019230769231" style="3" customWidth="1"/>
+    <col min="34" max="34" width="27.6538461538462" style="3" customWidth="1"/>
+    <col min="35" max="35" width="27.7788461538462" style="3" customWidth="1"/>
+    <col min="36" max="36" width="24.0769230769231" style="3" customWidth="1"/>
+    <col min="37" max="39" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31" customHeight="1" spans="1:22">
+    <row r="1" ht="31" customHeight="1" spans="1:20">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1618,159 +1588,141 @@
       <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+    </row>
+    <row r="2" ht="154" customHeight="1" spans="1:43">
+      <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" ht="154" customHeight="1" spans="1:45">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="T2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="R2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
       <c r="AP2" s="3"/>
       <c r="AQ2" s="3"/>
-      <c r="AR2" s="3"/>
-      <c r="AS2" s="3"/>
     </row>
-    <row r="3" ht="27" customHeight="1" spans="1:22">
+    <row r="3" ht="27" customHeight="1" spans="1:20">
       <c r="A3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="Q3" t="s">
         <v>54</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="S3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="P3" s="3" t="s">
+    </row>
+    <row r="4" ht="110" customHeight="1" spans="1:20">
+      <c r="A4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="B4" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="U3" t="s">
-        <v>61</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" ht="110" customHeight="1" spans="1:21">
-      <c r="A4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="C4" s="1">
         <v>12.3</v>
@@ -1779,76 +1731,62 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="K4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="P4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="Q4" t="s">
         <v>71</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="R4" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="P4" s="5" t="s">
+    </row>
+    <row r="5" ht="49" customHeight="1" spans="1:17">
+      <c r="A5" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>76</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="U4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" ht="49" customHeight="1" spans="1:21">
-      <c r="A5" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="F5" s="1">
         <v>3</v>
       </c>
       <c r="Q5" s="7"/>
-      <c r="U5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="21:21">
-      <c r="U6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="21:21">
-      <c r="U7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
